--- a/AtchisonRegime/Outputs/Aust/ASX300_Real_Estate/df_regEquityReturns_ASX300_Real_Estate.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Real_Estate/df_regEquityReturns_ASX300_Real_Estate.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,7 +5659,7 @@
         <v>-0.9726698406613064</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1460332201527155</v>
+        <v>0.1241894196525952</v>
       </c>
       <c r="D92" t="b">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>-0.930850647666511</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2388191536463469</v>
+        <v>0.2339228301603335</v>
       </c>
       <c r="D93" t="b">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>-0.8890737992235942</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2406013064670542</v>
+        <v>0.2370619522653315</v>
       </c>
       <c r="D94" t="b">
         <v>0</v>
@@ -5830,7 +5830,7 @@
         <v>-1.090435517906162</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2007569734303624</v>
+        <v>0.1988546216055985</v>
       </c>
       <c r="D95" t="b">
         <v>0</v>
@@ -5887,7 +5887,7 @@
         <v>-1.28973601261699</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1400914415231331</v>
+        <v>0.1425534339131948</v>
       </c>
       <c r="D96" t="b">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>-1.487030325470401</v>
       </c>
       <c r="C97" t="n">
-        <v>0.08697420027797154</v>
+        <v>0.0881118604449648</v>
       </c>
       <c r="D97" t="b">
         <v>0</v>
@@ -6001,7 +6001,7 @@
         <v>-1.508648286865362</v>
       </c>
       <c r="C98" t="n">
-        <v>0.04458779450515634</v>
+        <v>0.05049734109636209</v>
       </c>
       <c r="D98" t="b">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>-1.530614951002829</v>
       </c>
       <c r="C99" t="n">
-        <v>0.03030594341745388</v>
+        <v>0.05226649969174183</v>
       </c>
       <c r="D99" t="b">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         <v>-1.552867908392353</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04619714416039293</v>
+        <v>0.06685384186450997</v>
       </c>
       <c r="D100" t="b">
         <v>0</v>
@@ -6172,7 +6172,7 @@
         <v>-1.4620752903488</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03127296425735279</v>
+        <v>0.0775006846619135</v>
       </c>
       <c r="D101" t="b">
         <v>0</v>
@@ -6226,10 +6226,10 @@
         <v>45747</v>
       </c>
       <c r="B102" t="n">
-        <v>-1.380584681996217</v>
+        <v>-1.383605099136776</v>
       </c>
       <c r="C102" t="n">
-        <v>0.04765921338260101</v>
+        <v>0.09199325928623918</v>
       </c>
       <c r="D102" t="b">
         <v>0</v>
@@ -6275,6 +6275,63 @@
         <v>90.66567558385978</v>
       </c>
       <c r="Q102" t="n">
+        <v>98.86480404607528</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B103" t="n">
+        <v>-1.312657793185081</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.08562355455682437</v>
+      </c>
+      <c r="D103" t="b">
+        <v>0</v>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-4.83918964960496</v>
+      </c>
+      <c r="G103" t="n">
+        <v>144804.9919440151</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>-4.83918964960496</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>160.4508049750852</v>
+      </c>
+      <c r="O103" t="n">
+        <v>108.4780223680335</v>
+      </c>
+      <c r="P103" t="n">
+        <v>90.66567558385978</v>
+      </c>
+      <c r="Q103" t="n">
         <v>98.86480404607528</v>
       </c>
     </row>
